--- a/Income Tax Downloaded/ITR Bot/JATIN_CBXPJ6916L/Report_CBXPJ6916L.xlsx
+++ b/Income Tax Downloaded/ITR Bot/JATIN_CBXPJ6916L/Report_CBXPJ6916L.xlsx
@@ -43,7 +43,7 @@
     <t>JATIN_CBXPJ6916L</t>
   </si>
   <si>
-    <t>2026-05-18 16:49:17</t>
+    <t>2026-05-19 12:20:15</t>
   </si>
 </sst>
 </file>
